--- a/data/availability/projects/pre-developments/ivoire-east.xlsx
+++ b/data/availability/projects/pre-developments/ivoire-east.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for ivoire-east</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -737,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +847,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -959,7 +969,6 @@
       <c r="G2" t="n">
         <v>233</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1138,7 +1147,6 @@
       <c r="G5" t="n">
         <v>312</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1195,7 +1203,6 @@
       <c r="G6" t="n">
         <v>117</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1206,7 +1213,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1252,7 +1259,6 @@
       <c r="G7" t="n">
         <v>161</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1263,7 +1269,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1309,7 +1315,6 @@
       <c r="G8" t="n">
         <v>266</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1320,7 +1325,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
